--- a/artfynd/A 63227-2023 artfynd.xlsx
+++ b/artfynd/A 63227-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63227-2023 artfynd.xlsx
+++ b/artfynd/A 63227-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114594383</v>
+        <v>114594381</v>
       </c>
       <c r="B2" t="n">
-        <v>56183</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -801,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114594381</v>
+        <v>114594383</v>
       </c>
       <c r="B3" t="n">
-        <v>56178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -930,12 +920,7 @@
         <v>114594382</v>
       </c>
       <c r="B4" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,12 +1041,7 @@
         <v>114594380</v>
       </c>
       <c r="B5" t="n">
-        <v>56185</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,12 +1162,7 @@
         <v>115822744</v>
       </c>
       <c r="B6" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 63227-2023 artfynd.xlsx
+++ b/artfynd/A 63227-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114594381</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114594383</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114594382</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114594380</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,8 +1278,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115822744</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>